--- a/scorecard.xlsx
+++ b/scorecard.xlsx
@@ -865,19 +865,31 @@
       <c r="D5" s="11" t="n">
         <v>0.15</v>
       </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
+      <c r="E5" s="7" t="n">
+        <v>-25.1</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>-23.7</v>
+      </c>
       <c r="G5" s="12">
         <f>IFERROR((E5-F5)/ABS(F5),"")</f>
         <v/>
       </c>
-      <c r="H5" s="7" t="n"/>
+      <c r="H5" s="7" t="n">
+        <v>-1</v>
+      </c>
       <c r="I5" s="8">
         <f>IF(H5="","",D5*H5)</f>
         <v/>
       </c>
-      <c r="J5" s="7" t="inlineStr"/>
-      <c r="K5" s="13" t="n"/>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>变化 -1.40pp，温和恶化</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>46295</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -898,19 +910,31 @@
       <c r="D6" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
+      <c r="E6" s="7" t="n">
+        <v>-13.2</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>-12.1</v>
+      </c>
       <c r="G6" s="12">
         <f>IFERROR((E6-F6)/ABS(F6),"")</f>
         <v/>
       </c>
-      <c r="H6" s="7" t="n"/>
+      <c r="H6" s="7" t="n">
+        <v>-1</v>
+      </c>
       <c r="I6" s="8">
         <f>IF(H6="","",D6*H6)</f>
         <v/>
       </c>
-      <c r="J6" s="7" t="inlineStr"/>
-      <c r="K6" s="13" t="n"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>变化 -1.10pp，温和恶化</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="n">
+        <v>46295</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -931,19 +955,31 @@
       <c r="D7" s="11" t="n">
         <v>0.15</v>
       </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
+      <c r="E7" s="7" t="n">
+        <v>-15.07</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>-12.87</v>
+      </c>
       <c r="G7" s="12">
         <f>IFERROR((E7-F7)/ABS(F7),"")</f>
         <v/>
       </c>
-      <c r="H7" s="7" t="n"/>
+      <c r="H7" s="7" t="n">
+        <v>-2</v>
+      </c>
       <c r="I7" s="8">
         <f>IF(H7="","",D7*H7)</f>
         <v/>
       </c>
-      <c r="J7" s="7" t="inlineStr"/>
-      <c r="K7" s="13" t="n"/>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>变化 -2.20pp，显著恶化</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>46203</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -964,18 +1000,26 @@
       <c r="D8" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="E8" s="7" t="n"/>
+      <c r="E8" s="7" t="n">
+        <v>-4.32</v>
+      </c>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="12">
         <f>IFERROR((E8-F8)/ABS(F8),"")</f>
         <v/>
       </c>
-      <c r="H8" s="7" t="n"/>
+      <c r="H8" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="I8" s="8">
         <f>IF(H8="","",D8*H8)</f>
         <v/>
       </c>
-      <c r="J8" s="7" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>8月单月出口额同比 -4.32%，明显好于 1—8月累计的 -7.72%，降幅收窄即边际改善；因缺 7 月单月值无法算严格变化，按定性 +1 处理（人工判断 2026-10-27）</t>
+        </is>
+      </c>
       <c r="K8" s="13" t="n"/>
     </row>
     <row r="9">
@@ -997,18 +1041,26 @@
       <c r="D9" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="E9" s="7" t="n"/>
+      <c r="E9" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="12">
         <f>IFERROR((E9-F9)/ABS(F9),"")</f>
         <v/>
       </c>
-      <c r="H9" s="7" t="n"/>
+      <c r="H9" s="7" t="n">
+        <v>-2</v>
+      </c>
       <c r="I9" s="8">
         <f>IF(H9="","",D9*H9)</f>
         <v/>
       </c>
-      <c r="J9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>定性档位 2/2（历史低位）：江西高安约7成、上高宜丰8-9成，但国内其它产区普遍不足50%，行业开窑率处于历史低位（人工判断 2026-10-27）</t>
+        </is>
+      </c>
       <c r="K9" s="13" t="n"/>
     </row>
     <row r="10">
@@ -1030,19 +1082,31 @@
       <c r="D10" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
+      <c r="E10" s="7" t="n">
+        <v>136.91</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>129.84</v>
+      </c>
       <c r="G10" s="12">
         <f>IFERROR((E10-F10)/ABS(F10),"")</f>
         <v/>
       </c>
-      <c r="H10" s="7" t="n"/>
+      <c r="H10" s="7" t="n">
+        <v>-2</v>
+      </c>
       <c r="I10" s="8">
         <f>IF(H10="","",D10*H10)</f>
         <v/>
       </c>
-      <c r="J10" s="7" t="inlineStr"/>
-      <c r="K10" s="13" t="n"/>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>变化 +7.07pp，显著恶化</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>46203</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1063,18 +1127,26 @@
       <c r="D11" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="E11" s="7" t="n"/>
+      <c r="E11" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="12">
         <f>IFERROR((E11-F11)/ABS(F11),"")</f>
         <v/>
       </c>
-      <c r="H11" s="7" t="n"/>
+      <c r="H11" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="I11" s="8">
         <f>IF(H11="","",D11*H11)</f>
         <v/>
       </c>
-      <c r="J11" s="7" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>无公开价格指数，按「定性档位法」：1档（涨价函广但落地存疑）→ +1。依据：8.29-9.5 七产区集中涨价函，但属煤价成本推动且终端难落地（人工判断 2026-10-27）</t>
+        </is>
+      </c>
       <c r="K11" s="13" t="n"/>
     </row>
     <row r="12">
@@ -1096,19 +1168,31 @@
       <c r="D12" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
+      <c r="E12" s="7" t="n">
+        <v>6749.4</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>6185.9</v>
+      </c>
       <c r="G12" s="12">
         <f>IFERROR((E12-F12)/ABS(F12),"")</f>
         <v/>
       </c>
-      <c r="H12" s="7" t="n"/>
+      <c r="H12" s="7" t="n">
+        <v>-2</v>
+      </c>
       <c r="I12" s="8">
         <f>IF(H12="","",D12*H12)</f>
         <v/>
       </c>
-      <c r="J12" s="7" t="inlineStr"/>
-      <c r="K12" s="13" t="n"/>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>变化 +563.50pp，显著恶化</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>46315</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1129,19 +1213,31 @@
       <c r="D13" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
+      <c r="E13" s="7" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>25.66</v>
+      </c>
       <c r="G13" s="12">
         <f>IFERROR((E13-F13)/ABS(F13),"")</f>
         <v/>
       </c>
-      <c r="H13" s="7" t="n"/>
+      <c r="H13" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="I13" s="8">
         <f>IF(H13="","",D13*H13)</f>
         <v/>
       </c>
-      <c r="J13" s="7" t="inlineStr"/>
-      <c r="K13" s="13" t="n"/>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>变化 +0.50pp，温和改善</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>46203</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1162,19 +1258,31 @@
       <c r="D14" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
+      <c r="E14" s="7" t="n">
+        <v>58.39</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>73.97</v>
+      </c>
       <c r="G14" s="12">
         <f>IFERROR((E14-F14)/ABS(F14),"")</f>
         <v/>
       </c>
-      <c r="H14" s="7" t="n"/>
+      <c r="H14" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="I14" s="8">
         <f>IF(H14="","",D14*H14)</f>
         <v/>
       </c>
-      <c r="J14" s="7" t="inlineStr"/>
-      <c r="K14" s="13" t="n"/>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>天数 73.97→58.39 降 15.6 天，但同期营收同比 -15.1%，分母缩水效应显著，不能直接视为回款改善，由 +2 下调至 +1（人工判断 2026-10-27）</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="n">
+        <v>46203</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -1195,18 +1303,26 @@
       <c r="D15" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="E15" s="7" t="n"/>
+      <c r="E15" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="12">
         <f>IFERROR((E15-F15)/ABS(F15),"")</f>
         <v/>
       </c>
-      <c r="H15" s="7" t="n"/>
+      <c r="H15" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="I15" s="8">
         <f>IF(H15="","",D15*H15)</f>
         <v/>
       </c>
-      <c r="J15" s="7" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>水平型指标，不适用变化法。Q3 政策强度 3/3 分（8·28全国性文件+一线放松），按「3分→+2」映射（人工判断 2026-10-27）</t>
+        </is>
+      </c>
       <c r="K15" s="13" t="n"/>
     </row>
     <row r="16">
@@ -1228,18 +1344,26 @@
       <c r="D16" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="E16" s="7" t="n"/>
+      <c r="E16" s="7" t="n">
+        <v>1</v>
+      </c>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="12">
         <f>IFERROR((E16-F16)/ABS(F16),"")</f>
         <v/>
       </c>
-      <c r="H16" s="7" t="n"/>
+      <c r="H16" s="7" t="n">
+        <v>-1</v>
+      </c>
       <c r="I16" s="8">
         <f>IF(H16="","",D16*H16)</f>
         <v/>
       </c>
-      <c r="J16" s="7" t="inlineStr"/>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>负向指标，定性档位 1/2：建筑卫生陶瓷纳入2026年度工业节能监察重点，多地环保管控叠加订单不足致停窑减产，但未见主产区大范围停限产（人工判断 2026-10-27）</t>
+        </is>
+      </c>
       <c r="K16" s="13" t="n"/>
     </row>
     <row r="17">
